--- a/static/OCs de Preceptores.xlsx
+++ b/static/OCs de Preceptores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\bruno\projects\proz-oc-m8\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{262CEFB5-E23A-4B46-9A9E-E5BD88609A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A97E67C-56E4-49F5-AD0D-F0A232F12B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{DDD3F3E3-D987-46A7-8E58-F4A558E67861}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{DDD3F3E3-D987-46A7-8E58-F4A558E67861}"/>
   </bookViews>
   <sheets>
     <sheet name="Cadastro" sheetId="1" state="hidden" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Unidade</t>
   </si>
@@ -147,7 +147,16 @@
     <t>DEZEMBRO</t>
   </si>
   <si>
-    <t>v1</t>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Preceptor</t>
   </si>
 </sst>
 </file>
@@ -157,7 +166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,16 +181,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -189,27 +212,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8"/>
+      </left>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8"/>
+      </left>
+      <right style="thin">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -220,40 +307,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D8221944-4647-4362-A157-F22A5D6DE55A}" name="unidade" displayName="unidade" ref="C1:C20" totalsRowShown="0">
-  <autoFilter ref="C1:C20" xr:uid="{D8221944-4647-4362-A157-F22A5D6DE55A}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{642F2F98-2804-41F6-9952-94B89CB97859}" name="Unidade"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{462EE8CA-82D4-4087-8698-74D207241AE6}" name="observação" displayName="observação" ref="E1:E13" totalsRowShown="0">
-  <autoFilter ref="E1:E13" xr:uid="{462EE8CA-82D4-4087-8698-74D207241AE6}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{72BC5B96-E9A3-4992-B5DA-BF71C4565CC0}" name="Observação"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7EF5B21E-B592-47D0-8324-FF6C8CF390CD}" name="OCs" displayName="OCs" ref="A1:E3" totalsRowShown="0">
-  <autoFilter ref="A1:E3" xr:uid="{7EF5B21E-B592-47D0-8324-FF6C8CF390CD}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F78810D9-BF9A-4D21-96B5-1801A99781B8}" name="Unidade"/>
-    <tableColumn id="2" xr3:uid="{586884D5-2D7F-4B90-95DA-3055313D061E}" name="ID Fornecedor"/>
-    <tableColumn id="3" xr3:uid="{877DAFD6-646C-4A91-B84E-CEA2A177C953}" name="Valor" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{4CBC6B64-E01C-4E74-B435-972F25D81E7A}" name="Vencimento" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{67F074A4-7ED6-4EF0-9CB9-2C14A3288A5C}" name="Observação"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,209 +627,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71EA7273-AB5E-4134-BF07-7AF0325DDFEC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
+      <c r="G1" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+      <c r="G2" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+      <c r="G3" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
+      <c r="C17" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
+      <c r="C18" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
+      <c r="C19" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
+      <c r="C20" s="13" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59D9039-3A7F-4F10-A3E2-E7C62491D914}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="3"/>
-    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A3" xr:uid="{E460CF34-3711-4588-80D6-C144DCBFA894}">
-      <formula1>INDIRECT("unidade[Unidade]")</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3" xr:uid="{EA4166D0-20DA-47B5-A8C6-221DF99FD083}">
-      <formula1>INDIRECT("observação[Observação]")</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B60813E3-4923-4054-BC96-F15105ABA461}">
+          <x14:formula1>
+            <xm:f>Cadastro!$C$2:$C$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4A3A85FE-7DE9-47BA-8849-54A9B7E8AE74}">
+          <x14:formula1>
+            <xm:f>Cadastro!$E$2:$E$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DF13E20E-BCC2-4BB0-8330-751A55429946}">
+          <x14:formula1>
+            <xm:f>Cadastro!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>